--- a/RayatAuto-data-template.xlsx
+++ b/RayatAuto-data-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\البرامج المطورة\من الفايز - تحت المراجعة\POWERAUTO\RayatAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530DE085-B530-4F97-8F7A-D81D32484678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA3F476-C4F9-46FA-A968-3BA68EBF92C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="893" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,6 +31,9 @@
     <sheet name="4) تصفير الحد الأدنى" sheetId="17" r:id="rId16"/>
     <sheet name="5) تعديل تسجيل" sheetId="16" r:id="rId17"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10) تخصيص شعب'!$J$2:$M$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -49,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="380">
   <si>
     <t>الفكرة</t>
   </si>
@@ -526,16 +529,695 @@
   <si>
     <t>عمود واحد: رقم المتدرب، رقم تدريبي لكل سطر. تعدل الإضافة ساعات الحد الأدنى إلى صفر.</t>
   </si>
+  <si>
+    <t>اسم القسم</t>
+  </si>
+  <si>
+    <t>اسم التخصص</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>قسم التقنية الكهربائية</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>تقنية الآلات كهربائية</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>تقنية القوى كهربائية</t>
+  </si>
+  <si>
+    <t>0103</t>
+  </si>
+  <si>
+    <t>كهربائي توزيع</t>
+  </si>
+  <si>
+    <t>0104</t>
+  </si>
+  <si>
+    <t>كهربائي خطوط هوائية</t>
+  </si>
+  <si>
+    <t>0105</t>
+  </si>
+  <si>
+    <t>كهربائي خطوط أرضية</t>
+  </si>
+  <si>
+    <t>0106</t>
+  </si>
+  <si>
+    <t>هندسة القوى والآلات الكهربائية</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>مشغل لوحة التحكم الكهربائية</t>
+  </si>
+  <si>
+    <t>0108</t>
+  </si>
+  <si>
+    <t>تقنية الطاقة المتجددة</t>
+  </si>
+  <si>
+    <t>0109</t>
+  </si>
+  <si>
+    <t>الكهرباء الإنشائية</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>الكهرباء الصناعية</t>
+  </si>
+  <si>
+    <t>0111</t>
+  </si>
+  <si>
+    <t>المصاعد الكهربائية</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>قسم التقنية الميكانيكية</t>
+  </si>
+  <si>
+    <t>0201</t>
+  </si>
+  <si>
+    <t>تقنية التصنيع</t>
+  </si>
+  <si>
+    <t>0202</t>
+  </si>
+  <si>
+    <t>تقنية المحركات ومركبات</t>
+  </si>
+  <si>
+    <t>0203</t>
+  </si>
+  <si>
+    <t>تقنية التبريد وتكييف الهواء</t>
+  </si>
+  <si>
+    <t>0204</t>
+  </si>
+  <si>
+    <t>تقنية الكهرباء والكترونيات الم</t>
+  </si>
+  <si>
+    <t>0205</t>
+  </si>
+  <si>
+    <t>المعدات ثقيلة</t>
+  </si>
+  <si>
+    <t>0206</t>
+  </si>
+  <si>
+    <t>الأنظمة الهيدروليكية والنيومات</t>
+  </si>
+  <si>
+    <t>0207</t>
+  </si>
+  <si>
+    <t>اللحام</t>
+  </si>
+  <si>
+    <t>0208</t>
+  </si>
+  <si>
+    <t>الصفائح المعدنية</t>
+  </si>
+  <si>
+    <t>0209</t>
+  </si>
+  <si>
+    <t>صيانة الآلات الميكانيكية</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>تشغيل آلات الإنتاج</t>
+  </si>
+  <si>
+    <t>0211</t>
+  </si>
+  <si>
+    <t>تشغيل آلات التحكم الرقمي</t>
+  </si>
+  <si>
+    <t>0212</t>
+  </si>
+  <si>
+    <t>هندسة المحركات والمركبات التطب</t>
+  </si>
+  <si>
+    <t>0213</t>
+  </si>
+  <si>
+    <t>مركبات النقل وميكانيكا سيارات</t>
+  </si>
+  <si>
+    <t>0214</t>
+  </si>
+  <si>
+    <t>تشكيل و تركيب الألمنيوم</t>
+  </si>
+  <si>
+    <t>0215</t>
+  </si>
+  <si>
+    <t>النجارة العامة</t>
+  </si>
+  <si>
+    <t>0216</t>
+  </si>
+  <si>
+    <t>سمكرة المركبات</t>
+  </si>
+  <si>
+    <t>0217</t>
+  </si>
+  <si>
+    <t>دهان وتلميع المركبات</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>قسم الحاسب وتقنية المعلومات</t>
+  </si>
+  <si>
+    <t>0301</t>
+  </si>
+  <si>
+    <t>تقنية البرمجة وتطوير الويب</t>
+  </si>
+  <si>
+    <t>0302</t>
+  </si>
+  <si>
+    <t>تقنية الدعم الفني للحاسب</t>
+  </si>
+  <si>
+    <t>0303</t>
+  </si>
+  <si>
+    <t>تقنية شبكات الحاسب</t>
+  </si>
+  <si>
+    <t>0304</t>
+  </si>
+  <si>
+    <t>تقنية إدارة أنظمة الشبكات</t>
+  </si>
+  <si>
+    <t>0305</t>
+  </si>
+  <si>
+    <t>تقنية الوسائط المتعددة وتقنيات</t>
+  </si>
+  <si>
+    <t>0306</t>
+  </si>
+  <si>
+    <t>دعم أنظمة شبكات الحاسب</t>
+  </si>
+  <si>
+    <t>0307</t>
+  </si>
+  <si>
+    <t>الحاسب الآلي</t>
+  </si>
+  <si>
+    <t>0308</t>
+  </si>
+  <si>
+    <t>الأمن السيبراني</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>قسم تقنية الاعمال (التقنية الإدارية قديمًا)</t>
+  </si>
+  <si>
+    <t>0403</t>
+  </si>
+  <si>
+    <t>تقنيات الاعمال المكتبية</t>
+  </si>
+  <si>
+    <t>0404</t>
+  </si>
+  <si>
+    <t>تقنيات محاسبية</t>
+  </si>
+  <si>
+    <t>0405</t>
+  </si>
+  <si>
+    <t>تقنية التسويق والابتكار</t>
+  </si>
+  <si>
+    <t>0406</t>
+  </si>
+  <si>
+    <t>إدارة المستودعات</t>
+  </si>
+  <si>
+    <t>0407</t>
+  </si>
+  <si>
+    <t>تقنية الموارد البشرية</t>
+  </si>
+  <si>
+    <t>0408</t>
+  </si>
+  <si>
+    <t>تقنيات التأمين والمخاطر</t>
+  </si>
+  <si>
+    <t>0409</t>
+  </si>
+  <si>
+    <t>تقنية الاعمال</t>
+  </si>
+  <si>
+    <t>0410</t>
+  </si>
+  <si>
+    <t>تقنية التجارة الالكترونية</t>
+  </si>
+  <si>
+    <t>0411</t>
+  </si>
+  <si>
+    <t>تقنية الخدمات اللوجستية</t>
+  </si>
+  <si>
+    <t>0419</t>
+  </si>
+  <si>
+    <t>تقنية التصميم الداخلي</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>قسم التقنية الالكترونية</t>
+  </si>
+  <si>
+    <t>0501</t>
+  </si>
+  <si>
+    <t>تقنية الإلكترونيات وأنظمة التح</t>
+  </si>
+  <si>
+    <t>0502</t>
+  </si>
+  <si>
+    <t>تقنية الأجهزة الطبية</t>
+  </si>
+  <si>
+    <t>0503</t>
+  </si>
+  <si>
+    <t>تقنية أجهزة وآلات دقيقة</t>
+  </si>
+  <si>
+    <t>0504</t>
+  </si>
+  <si>
+    <t>الإلكترونيات</t>
+  </si>
+  <si>
+    <t>0505</t>
+  </si>
+  <si>
+    <t>صيانة الأجهزة الذكية</t>
+  </si>
+  <si>
+    <t>0506</t>
+  </si>
+  <si>
+    <t>تقنية نظارات</t>
+  </si>
+  <si>
+    <t>0507</t>
+  </si>
+  <si>
+    <t>تقنية الروبوتات والذكاء الاصطن</t>
+  </si>
+  <si>
+    <t>0508</t>
+  </si>
+  <si>
+    <t>تقنية الميكاترونيكس</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>قسم التقنية المدنية والمعمارية</t>
+  </si>
+  <si>
+    <t>0601</t>
+  </si>
+  <si>
+    <t>تقنية الانشاءات المدنية</t>
+  </si>
+  <si>
+    <t>0602</t>
+  </si>
+  <si>
+    <t>تقنية الانشاءات المعمارية</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>تقنية المساحة</t>
+  </si>
+  <si>
+    <t>0604</t>
+  </si>
+  <si>
+    <t>التشييد</t>
+  </si>
+  <si>
+    <t>0605</t>
+  </si>
+  <si>
+    <t>الرسم المعماري</t>
+  </si>
+  <si>
+    <t>0606</t>
+  </si>
+  <si>
+    <t>التمديدات الصحية</t>
+  </si>
+  <si>
+    <t>0607</t>
+  </si>
+  <si>
+    <t>المراقبة المعمارية</t>
+  </si>
+  <si>
+    <t>0608</t>
+  </si>
+  <si>
+    <t>المراقبة المدنية</t>
+  </si>
+  <si>
+    <t>0609</t>
+  </si>
+  <si>
+    <t>الهندسة المدنية التطبيقية</t>
+  </si>
+  <si>
+    <t>0610</t>
+  </si>
+  <si>
+    <t>الهندسة المعمارية التطبيقية</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>قسم التقنية الكيميائية</t>
+  </si>
+  <si>
+    <t>0701</t>
+  </si>
+  <si>
+    <t>تقنية الانتاج الكيميائي</t>
+  </si>
+  <si>
+    <t>0702</t>
+  </si>
+  <si>
+    <t>تقنية المختبرات الكيميائية</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>قسم تقنية الاتصالات</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>تقنية الاتصالات</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>قسم تقنية الغذاء</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>تقنية التصنيع الغذائي</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>قسم تقنية السياحة والضيافة</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>السفر والسياحة</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>الفندقة</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>إنتاج الطعام (الطهي)</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>خدمة الطعام (الضيافة)</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>خدمات الحج والعمرة</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>الارشاد السياحي</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>إدارة الفعاليات</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>إدارة الضيافة</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>قسم تقنية البيئة</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>تقنية السلامة والصحة المهنية</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>تقنية حماية البيئة</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>سلامة الاغذية</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>قسم التقنية الخاصة</t>
+  </si>
+  <si>
+    <t>1301</t>
+  </si>
+  <si>
+    <t>تطبيقات مكتبية للمعوقين سمعيا</t>
+  </si>
+  <si>
+    <t>1302</t>
+  </si>
+  <si>
+    <t>تطبيقات مكتبية للمعوقين بصريا</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>1401</t>
+  </si>
+  <si>
+    <t>تقنية الإنتاج الغذائي</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>تقنية تصميم وتصنيع الأزياء</t>
+  </si>
+  <si>
+    <t>1502</t>
+  </si>
+  <si>
+    <t>تقنية إنتاج وتصنيع الأزياء</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>تقنية الموضة وتصميم الأزياء</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>الخياطة الرجالية</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>قسم تقنية التزيين والتجميل</t>
+  </si>
+  <si>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>تقنية العناية بالشعر</t>
+  </si>
+  <si>
+    <t>1603</t>
+  </si>
+  <si>
+    <t>تقنية التجميل والعناية بالبشرة</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>التزيين النسائي - التجميل</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>الحلاقة والتجميل</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>قسم تقنية الانتاج الإعلامي</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>التصوير الضوئي</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>التصميم والطباعة الرقمية</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>الطباعة الآلية</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>التصوير الضوئي - الفوتوغرافي</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>التصميم و التجهيز الطباعي</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>التجليد</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>طباعة الأوفست</t>
+  </si>
+  <si>
+    <t>ابحث بالقسم أو التخصص</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0000000"/>
     <numFmt numFmtId="165" formatCode="0000000000"/>
+    <numFmt numFmtId="168" formatCode="0000;\-0000;0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,8 +1354,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF13544C"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -726,8 +1433,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF5F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF186E64"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -811,12 +1529,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D6D2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9D6D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D6D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D6D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9D6D2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D6D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D6D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D6D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D6D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9D6D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9D6D2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9D6D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -885,79 +1655,86 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -970,60 +1747,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
+    <xf numFmtId="168" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
@@ -1044,6 +1842,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF186E64"/>
+      <color rgb="FF1B7E72"/>
       <color rgb="FF2FB0A3"/>
       <color rgb="FFE4F1E6"/>
     </mruColors>
@@ -1356,36 +2156,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1398,576 +2198,566 @@
       <c r="H4" s="5"/>
     </row>
     <row r="6" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8" s="9" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8" s="9" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
     </row>
     <row r="26" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="53" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="53" t="s">
+      <c r="E26" s="57"/>
+      <c r="F26" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-    </row>
-    <row r="27" spans="1:8" s="56" customFormat="1" ht="5.4" x14ac:dyDescent="0.15"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+    </row>
+    <row r="27" spans="1:8" s="25" customFormat="1" ht="5.4" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
     </row>
     <row r="29" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="48"/>
-      <c r="C29" s="57" t="str">
+      <c r="B29" s="62"/>
+      <c r="C29" s="26" t="str">
         <f t="shared" ref="C29:C39" si="0">HYPERLINK("#'" &amp; A29 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="49" t="s">
+      <c r="E29" s="43"/>
+      <c r="F29" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="58"/>
-      <c r="H29" s="59"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="49"/>
     </row>
     <row r="30" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="60" t="str">
+      <c r="B30" s="36"/>
+      <c r="C30" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D30" s="40" t="s">
+      <c r="D30" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="30" t="s">
+      <c r="E30" s="32"/>
+      <c r="F30" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="61"/>
-      <c r="H30" s="62"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="45"/>
     </row>
     <row r="31" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="31"/>
-      <c r="C31" s="63" t="str">
+      <c r="C31" s="28" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
       <c r="D31" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="29" t="s">
+      <c r="E31" s="32"/>
+      <c r="F31" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="45"/>
     </row>
     <row r="32" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="60" t="str">
+      <c r="B32" s="36"/>
+      <c r="C32" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="30" t="s">
+      <c r="E32" s="32"/>
+      <c r="F32" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="61"/>
-      <c r="H32" s="62"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="45"/>
     </row>
     <row r="33" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
         <v>67</v>
       </c>
       <c r="B33" s="31"/>
-      <c r="C33" s="63" t="str">
+      <c r="C33" s="28" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
       <c r="D33" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="29" t="s">
+      <c r="E33" s="32"/>
+      <c r="F33" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G33" s="61"/>
-      <c r="H33" s="62"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="45"/>
     </row>
     <row r="34" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="60" t="str">
+      <c r="B34" s="36"/>
+      <c r="C34" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="30" t="s">
+      <c r="E34" s="32"/>
+      <c r="F34" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="45"/>
     </row>
     <row r="35" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
         <v>78</v>
       </c>
       <c r="B35" s="31"/>
-      <c r="C35" s="63" t="str">
+      <c r="C35" s="28" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
       <c r="D35" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="29" t="s">
+      <c r="E35" s="32"/>
+      <c r="F35" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G35" s="61"/>
-      <c r="H35" s="62"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="45"/>
     </row>
     <row r="36" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="60" t="str">
+      <c r="B36" s="36"/>
+      <c r="C36" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="30" t="s">
+      <c r="E36" s="32"/>
+      <c r="F36" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G36" s="61"/>
-      <c r="H36" s="62"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="45"/>
     </row>
     <row r="37" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
         <v>82</v>
       </c>
       <c r="B37" s="31"/>
-      <c r="C37" s="63" t="str">
+      <c r="C37" s="28" t="str">
         <f t="shared" ref="C37:C38" si="1">HYPERLINK("#'" &amp; A37 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
       <c r="D37" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="61"/>
-      <c r="F37" s="29" t="s">
+      <c r="E37" s="32"/>
+      <c r="F37" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G37" s="61"/>
-      <c r="H37" s="62"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="45"/>
     </row>
     <row r="38" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="31" t="s">
         <v>103</v>
       </c>
       <c r="B38" s="31"/>
-      <c r="C38" s="63" t="str">
+      <c r="C38" s="28" t="str">
         <f t="shared" si="1"/>
         <v>انتقل</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="61"/>
-      <c r="F38" s="30" t="s">
+      <c r="E38" s="32"/>
+      <c r="F38" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G38" s="61"/>
-      <c r="H38" s="62"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="45"/>
     </row>
     <row r="39" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="64" t="s">
+      <c r="A39" s="63" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="64"/>
-      <c r="C39" s="65" t="str">
+      <c r="B39" s="63"/>
+      <c r="C39" s="29" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
       <c r="D39" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="66"/>
-      <c r="F39" s="29" t="s">
+      <c r="E39" s="39"/>
+      <c r="F39" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G39" s="66"/>
-      <c r="H39" s="67"/>
-    </row>
-    <row r="40" spans="1:8" s="56" customFormat="1" ht="5.4" x14ac:dyDescent="0.15"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="61"/>
+    </row>
+    <row r="40" spans="1:8" s="25" customFormat="1" ht="5.4" x14ac:dyDescent="0.15"/>
     <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="68"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="35"/>
     </row>
     <row r="42" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
         <v>114</v>
       </c>
       <c r="B42" s="31"/>
-      <c r="C42" s="63" t="str">
+      <c r="C42" s="28" t="str">
         <f t="shared" ref="C42:C46" si="2">HYPERLINK("#'" &amp; A42 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
       <c r="D42" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="61"/>
-      <c r="F42" s="29" t="s">
+      <c r="E42" s="32"/>
+      <c r="F42" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
     </row>
     <row r="43" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="60" t="str">
+      <c r="B43" s="36"/>
+      <c r="C43" s="27" t="str">
         <f t="shared" ref="C43:C44" si="3">HYPERLINK("#'" &amp; A43 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
-      <c r="D43" s="30" t="s">
+      <c r="D43" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="61"/>
-      <c r="F43" s="30" t="s">
+      <c r="E43" s="32"/>
+      <c r="F43" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
     </row>
     <row r="44" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="31" t="s">
         <v>119</v>
       </c>
       <c r="B44" s="31"/>
-      <c r="C44" s="63" t="str">
+      <c r="C44" s="28" t="str">
         <f t="shared" si="3"/>
         <v>انتقل</v>
       </c>
       <c r="D44" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="61"/>
-      <c r="F44" s="29" t="s">
+      <c r="E44" s="32"/>
+      <c r="F44" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
     </row>
     <row r="45" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="30"/>
-      <c r="C45" s="60" t="str">
+      <c r="B45" s="36"/>
+      <c r="C45" s="27" t="str">
         <f t="shared" si="2"/>
         <v>انتقل</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D45" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="61"/>
-      <c r="F45" s="30" t="s">
+      <c r="E45" s="32"/>
+      <c r="F45" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
     </row>
     <row r="46" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="31" t="s">
         <v>122</v>
       </c>
       <c r="B46" s="31"/>
-      <c r="C46" s="63" t="str">
+      <c r="C46" s="28" t="str">
         <f t="shared" si="2"/>
         <v>انتقل</v>
       </c>
       <c r="D46" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="61"/>
-      <c r="F46" s="29" t="s">
+      <c r="E46" s="32"/>
+      <c r="F46" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
     </row>
     <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
+      <c r="A48" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
     </row>
     <row r="49" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
     </row>
     <row r="50" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="37" t="s">
@@ -1982,34 +2772,61 @@
       <c r="H50" s="38"/>
     </row>
     <row r="52" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A7:H8"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="A50:H50"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="A48:H49"/>
@@ -2026,48 +2843,21 @@
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="F38:H38"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A7:H8"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:H45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A50" r:id="rId1" display="🔗 صفحة المشروع (مرجع دائم): https://myalsh2030.github.io/rayatauto-firefox/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2092,22 +2882,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="41"/>
     </row>
     <row r="2" spans="1:2" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="28"/>
+      <c r="B2" s="41"/>
     </row>
     <row r="3" spans="1:2" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="28"/>
+      <c r="B3" s="41"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
@@ -2919,47 +3709,98 @@
   <sheetPr codeName="ورقة16">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M98"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" customWidth="1"/>
-    <col min="4" max="4" width="14.8984375" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="5.3984375" customWidth="1"/>
-    <col min="7" max="7" width="44.19921875" customWidth="1"/>
-    <col min="8" max="8" width="22.09765625" customWidth="1"/>
+    <col min="1" max="1" width="14" style="71" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" style="71" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="71" customWidth="1"/>
+    <col min="4" max="4" width="14.8984375" style="84" customWidth="1"/>
+    <col min="5" max="5" width="16" style="71" customWidth="1"/>
+    <col min="6" max="6" width="3.296875" style="71" customWidth="1"/>
+    <col min="7" max="7" width="40" style="71" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="71" customWidth="1"/>
+    <col min="9" max="9" width="3.296875" style="71" customWidth="1"/>
+    <col min="10" max="10" width="11" style="71" customWidth="1"/>
+    <col min="11" max="11" width="34" style="71" customWidth="1"/>
+    <col min="12" max="12" width="12" style="71" customWidth="1"/>
+    <col min="13" max="13" width="38" style="71" customWidth="1"/>
+    <col min="14" max="16384" width="8.796875" style="71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:13" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-    </row>
-    <row r="2" spans="1:8" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="J1" s="79" t="s">
+        <v>379</v>
+      </c>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="81"/>
+    </row>
+    <row r="2" spans="1:13" s="73" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="J2" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="M2" s="74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="73" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-    </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="J3" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="K3" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="L3" s="75" t="s">
+        <v>158</v>
+      </c>
+      <c r="M3" s="76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="D4" s="71"/>
+      <c r="J4" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="K4" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="L4" s="77" t="s">
+        <v>160</v>
+      </c>
+      <c r="M4" s="78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>23</v>
       </c>
@@ -2975,8 +3816,20 @@
       <c r="E5" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="K5" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="L5" s="75" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="76" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
@@ -2986,20 +3839,32 @@
       <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="82">
         <v>209</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="68" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="K6" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="L6" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="M6" s="78" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
@@ -3009,232 +3874,1458 @@
       <c r="C7" s="7">
         <v>401</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="82">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="47"/>
-    </row>
-    <row r="8" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="69"/>
+      <c r="J7" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="K7" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="L7" s="75" t="s">
+        <v>166</v>
+      </c>
+      <c r="M7" s="76" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="D8" s="83"/>
       <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="K8" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="L8" s="77" t="s">
+        <v>168</v>
+      </c>
+      <c r="M8" s="78" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="D9" s="83"/>
       <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" s="75" t="s">
+        <v>170</v>
+      </c>
+      <c r="M9" s="76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="D10" s="83"/>
       <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="K10" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="L10" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="M10" s="78" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="D11" s="83"/>
       <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="K11" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="L11" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="M11" s="76" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="D12" s="83"/>
       <c r="E12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="K12" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="L12" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="M12" s="78" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="K13" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="L13" s="75" t="s">
+        <v>178</v>
+      </c>
+      <c r="M13" s="76" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K14" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="M14" s="78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="83"/>
       <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L15" s="75" t="s">
+        <v>184</v>
+      </c>
+      <c r="M15" s="76" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K16" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L16" s="77" t="s">
+        <v>186</v>
+      </c>
+      <c r="M16" s="78" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K17" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="M17" s="76" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K18" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L18" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="M18" s="78" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="D19" s="83"/>
       <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J19" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K19" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L19" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="M19" s="76" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="D20" s="83"/>
       <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J20" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K20" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L20" s="77" t="s">
+        <v>194</v>
+      </c>
+      <c r="M20" s="78" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="D21" s="83"/>
       <c r="E21" s="8"/>
-    </row>
-    <row r="22" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K21" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L21" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="M21" s="76" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="D22" s="83"/>
       <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J22" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K22" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L22" s="77" t="s">
+        <v>198</v>
+      </c>
+      <c r="M22" s="78" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="D23" s="83"/>
       <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J23" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L23" s="75" t="s">
+        <v>200</v>
+      </c>
+      <c r="M23" s="76" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
+      <c r="D24" s="83"/>
       <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J24" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K24" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L24" s="77" t="s">
+        <v>202</v>
+      </c>
+      <c r="M24" s="78" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="D25" s="83"/>
       <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K25" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" s="75" t="s">
+        <v>204</v>
+      </c>
+      <c r="M25" s="76" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+      <c r="D26" s="83"/>
       <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K26" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="M26" s="78" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="D27" s="83"/>
       <c r="E27" s="8"/>
-    </row>
-    <row r="28" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L27" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="M27" s="76" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="D28" s="83"/>
       <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L28" s="77" t="s">
+        <v>210</v>
+      </c>
+      <c r="M28" s="78" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="D29" s="83"/>
       <c r="E29" s="8"/>
-    </row>
-    <row r="30" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J29" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="K29" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L29" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="M29" s="76" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="D30" s="83"/>
       <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="K30" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="L30" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="M30" s="78" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="D31" s="83"/>
       <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J31" s="75" t="s">
+        <v>216</v>
+      </c>
+      <c r="K31" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="L31" s="75" t="s">
+        <v>218</v>
+      </c>
+      <c r="M31" s="76" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
+      <c r="D32" s="83"/>
       <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J32" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="K32" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="L32" s="77" t="s">
+        <v>220</v>
+      </c>
+      <c r="M32" s="78" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="D33" s="83"/>
       <c r="E33" s="8"/>
-    </row>
-    <row r="34" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J33" s="75" t="s">
+        <v>216</v>
+      </c>
+      <c r="K33" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="L33" s="75" t="s">
+        <v>222</v>
+      </c>
+      <c r="M33" s="76" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
+      <c r="D34" s="83"/>
       <c r="E34" s="8"/>
-    </row>
-    <row r="35" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="L34" s="77" t="s">
+        <v>224</v>
+      </c>
+      <c r="M34" s="78" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="83"/>
       <c r="E35" s="8"/>
-    </row>
-    <row r="36" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J35" s="75" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="L35" s="75" t="s">
+        <v>226</v>
+      </c>
+      <c r="M35" s="76" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="D36" s="83"/>
       <c r="E36" s="8"/>
-    </row>
-    <row r="37" spans="1:5" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J36" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="K36" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="L36" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="78" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="19.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="83"/>
       <c r="E37" s="8"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J37" s="75" t="s">
+        <v>216</v>
+      </c>
+      <c r="K37" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="L37" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="M37" s="76" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J38" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="K38" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="L38" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="M38" s="78" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="10"/>
+      <c r="J39" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="K39" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="L39" s="75" t="s">
+        <v>236</v>
+      </c>
+      <c r="M39" s="76" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J40" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="K40" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="L40" s="77" t="s">
+        <v>238</v>
+      </c>
+      <c r="M40" s="78" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J41" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="K41" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="L41" s="75" t="s">
+        <v>240</v>
+      </c>
+      <c r="M41" s="76" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J42" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="K42" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="L42" s="77" t="s">
+        <v>242</v>
+      </c>
+      <c r="M42" s="78" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J43" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="K43" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="L43" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="M43" s="76" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J44" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="K44" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="L44" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="M44" s="78" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J45" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="K45" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="L45" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="M45" s="76" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J46" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="K46" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="L46" s="77" t="s">
+        <v>250</v>
+      </c>
+      <c r="M46" s="78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J47" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="K47" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="L47" s="75" t="s">
+        <v>252</v>
+      </c>
+      <c r="M47" s="76" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="J48" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="K48" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="L48" s="77" t="s">
+        <v>254</v>
+      </c>
+      <c r="M48" s="78" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="49" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J49" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="K49" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="L49" s="75" t="s">
+        <v>258</v>
+      </c>
+      <c r="M49" s="76" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J50" s="77" t="s">
+        <v>256</v>
+      </c>
+      <c r="K50" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="L50" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="M50" s="78" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J51" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="K51" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="L51" s="75" t="s">
+        <v>262</v>
+      </c>
+      <c r="M51" s="76" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J52" s="77" t="s">
+        <v>256</v>
+      </c>
+      <c r="K52" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="L52" s="77" t="s">
+        <v>264</v>
+      </c>
+      <c r="M52" s="78" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J53" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="K53" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="L53" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="M53" s="76" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="54" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J54" s="77" t="s">
+        <v>256</v>
+      </c>
+      <c r="K54" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="L54" s="77" t="s">
+        <v>268</v>
+      </c>
+      <c r="M54" s="78" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="55" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J55" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="K55" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="L55" s="75" t="s">
+        <v>270</v>
+      </c>
+      <c r="M55" s="76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J56" s="77" t="s">
+        <v>256</v>
+      </c>
+      <c r="K56" s="78" t="s">
+        <v>257</v>
+      </c>
+      <c r="L56" s="77" t="s">
+        <v>272</v>
+      </c>
+      <c r="M56" s="78" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="57" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J57" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="K57" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="L57" s="75" t="s">
+        <v>276</v>
+      </c>
+      <c r="M57" s="76" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J58" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="K58" s="78" t="s">
+        <v>275</v>
+      </c>
+      <c r="L58" s="77" t="s">
+        <v>278</v>
+      </c>
+      <c r="M58" s="78" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="59" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J59" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="K59" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="L59" s="75" t="s">
+        <v>280</v>
+      </c>
+      <c r="M59" s="76" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="60" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J60" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="K60" s="78" t="s">
+        <v>275</v>
+      </c>
+      <c r="L60" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="M60" s="78" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="61" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J61" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="K61" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="L61" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="M61" s="76" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="62" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J62" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="K62" s="78" t="s">
+        <v>275</v>
+      </c>
+      <c r="L62" s="77" t="s">
+        <v>286</v>
+      </c>
+      <c r="M62" s="78" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="63" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J63" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="K63" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="L63" s="75" t="s">
+        <v>288</v>
+      </c>
+      <c r="M63" s="76" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="64" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J64" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="K64" s="78" t="s">
+        <v>275</v>
+      </c>
+      <c r="L64" s="77" t="s">
+        <v>290</v>
+      </c>
+      <c r="M64" s="78" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="65" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J65" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="K65" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="L65" s="75" t="s">
+        <v>292</v>
+      </c>
+      <c r="M65" s="76" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="66" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J66" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="K66" s="78" t="s">
+        <v>275</v>
+      </c>
+      <c r="L66" s="77" t="s">
+        <v>294</v>
+      </c>
+      <c r="M66" s="78" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="67" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J67" s="75" t="s">
+        <v>296</v>
+      </c>
+      <c r="K67" s="76" t="s">
+        <v>297</v>
+      </c>
+      <c r="L67" s="75" t="s">
+        <v>298</v>
+      </c>
+      <c r="M67" s="76" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J68" s="77" t="s">
+        <v>296</v>
+      </c>
+      <c r="K68" s="78" t="s">
+        <v>297</v>
+      </c>
+      <c r="L68" s="77" t="s">
+        <v>300</v>
+      </c>
+      <c r="M68" s="78" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="69" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J69" s="75" t="s">
+        <v>302</v>
+      </c>
+      <c r="K69" s="76" t="s">
+        <v>303</v>
+      </c>
+      <c r="L69" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="M69" s="76" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="70" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J70" s="77" t="s">
+        <v>306</v>
+      </c>
+      <c r="K70" s="78" t="s">
+        <v>307</v>
+      </c>
+      <c r="L70" s="77" t="s">
+        <v>308</v>
+      </c>
+      <c r="M70" s="78" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="71" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J71" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="K71" s="76" t="s">
+        <v>311</v>
+      </c>
+      <c r="L71" s="75" t="s">
+        <v>312</v>
+      </c>
+      <c r="M71" s="76" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J72" s="77" t="s">
+        <v>310</v>
+      </c>
+      <c r="K72" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="L72" s="77" t="s">
+        <v>314</v>
+      </c>
+      <c r="M72" s="78" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J73" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="K73" s="76" t="s">
+        <v>311</v>
+      </c>
+      <c r="L73" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="M73" s="76" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="74" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J74" s="77" t="s">
+        <v>310</v>
+      </c>
+      <c r="K74" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="L74" s="77" t="s">
+        <v>318</v>
+      </c>
+      <c r="M74" s="78" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="75" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J75" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="K75" s="76" t="s">
+        <v>311</v>
+      </c>
+      <c r="L75" s="75" t="s">
+        <v>320</v>
+      </c>
+      <c r="M75" s="76" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="76" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J76" s="77" t="s">
+        <v>310</v>
+      </c>
+      <c r="K76" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="L76" s="77" t="s">
+        <v>322</v>
+      </c>
+      <c r="M76" s="78" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="77" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J77" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="K77" s="76" t="s">
+        <v>311</v>
+      </c>
+      <c r="L77" s="75" t="s">
+        <v>324</v>
+      </c>
+      <c r="M77" s="76" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="78" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J78" s="77" t="s">
+        <v>310</v>
+      </c>
+      <c r="K78" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="L78" s="77" t="s">
+        <v>326</v>
+      </c>
+      <c r="M78" s="78" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="79" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J79" s="75" t="s">
+        <v>328</v>
+      </c>
+      <c r="K79" s="76" t="s">
+        <v>329</v>
+      </c>
+      <c r="L79" s="75" t="s">
+        <v>330</v>
+      </c>
+      <c r="M79" s="76" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="80" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J80" s="77" t="s">
+        <v>328</v>
+      </c>
+      <c r="K80" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="L80" s="77" t="s">
+        <v>332</v>
+      </c>
+      <c r="M80" s="78" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="81" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J81" s="75" t="s">
+        <v>328</v>
+      </c>
+      <c r="K81" s="76" t="s">
+        <v>329</v>
+      </c>
+      <c r="L81" s="75" t="s">
+        <v>334</v>
+      </c>
+      <c r="M81" s="76" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="82" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J82" s="77" t="s">
+        <v>336</v>
+      </c>
+      <c r="K82" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="L82" s="77" t="s">
+        <v>338</v>
+      </c>
+      <c r="M82" s="78" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="83" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J83" s="75" t="s">
+        <v>336</v>
+      </c>
+      <c r="K83" s="76" t="s">
+        <v>337</v>
+      </c>
+      <c r="L83" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="M83" s="76" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="84" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J84" s="77" t="s">
+        <v>342</v>
+      </c>
+      <c r="K84" s="78" t="s">
+        <v>307</v>
+      </c>
+      <c r="L84" s="77" t="s">
+        <v>343</v>
+      </c>
+      <c r="M84" s="78" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="85" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J85" s="75" t="s">
+        <v>345</v>
+      </c>
+      <c r="K85" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="L85" s="75" t="s">
+        <v>347</v>
+      </c>
+      <c r="M85" s="76" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="86" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J86" s="77" t="s">
+        <v>345</v>
+      </c>
+      <c r="K86" s="78" t="s">
+        <v>346</v>
+      </c>
+      <c r="L86" s="77" t="s">
+        <v>349</v>
+      </c>
+      <c r="M86" s="78" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J87" s="75" t="s">
+        <v>345</v>
+      </c>
+      <c r="K87" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="L87" s="75" t="s">
+        <v>351</v>
+      </c>
+      <c r="M87" s="76" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="88" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J88" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="K88" s="78" t="s">
+        <v>354</v>
+      </c>
+      <c r="L88" s="77" t="s">
+        <v>355</v>
+      </c>
+      <c r="M88" s="78" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="89" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J89" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="K89" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="L89" s="75" t="s">
+        <v>357</v>
+      </c>
+      <c r="M89" s="76" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="90" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J90" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="K90" s="78" t="s">
+        <v>354</v>
+      </c>
+      <c r="L90" s="77" t="s">
+        <v>359</v>
+      </c>
+      <c r="M90" s="78" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="91" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J91" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="K91" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="L91" s="75" t="s">
+        <v>361</v>
+      </c>
+      <c r="M91" s="76" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="92" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J92" s="77" t="s">
+        <v>363</v>
+      </c>
+      <c r="K92" s="78" t="s">
+        <v>364</v>
+      </c>
+      <c r="L92" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="M92" s="78" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="93" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J93" s="75" t="s">
+        <v>363</v>
+      </c>
+      <c r="K93" s="76" t="s">
+        <v>364</v>
+      </c>
+      <c r="L93" s="75" t="s">
+        <v>367</v>
+      </c>
+      <c r="M93" s="76" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="94" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J94" s="77" t="s">
+        <v>363</v>
+      </c>
+      <c r="K94" s="78" t="s">
+        <v>364</v>
+      </c>
+      <c r="L94" s="77" t="s">
+        <v>369</v>
+      </c>
+      <c r="M94" s="78" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="95" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J95" s="75" t="s">
+        <v>363</v>
+      </c>
+      <c r="K95" s="76" t="s">
+        <v>364</v>
+      </c>
+      <c r="L95" s="75" t="s">
+        <v>371</v>
+      </c>
+      <c r="M95" s="76" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="96" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J96" s="77" t="s">
+        <v>363</v>
+      </c>
+      <c r="K96" s="78" t="s">
+        <v>364</v>
+      </c>
+      <c r="L96" s="77" t="s">
+        <v>373</v>
+      </c>
+      <c r="M96" s="78" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="97" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J97" s="75" t="s">
+        <v>363</v>
+      </c>
+      <c r="K97" s="76" t="s">
+        <v>364</v>
+      </c>
+      <c r="L97" s="75" t="s">
+        <v>375</v>
+      </c>
+      <c r="M97" s="76" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="98" spans="10:13" x14ac:dyDescent="0.4">
+      <c r="J98" s="77" t="s">
+        <v>363</v>
+      </c>
+      <c r="K98" s="78" t="s">
+        <v>364</v>
+      </c>
+      <c r="L98" s="77" t="s">
+        <v>377</v>
+      </c>
+      <c r="M98" s="78" t="s">
+        <v>378</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <autoFilter ref="J2:M2" xr:uid="{3D513F8E-DFB4-4B13-9008-9C97DCB7F635}"/>
+  <mergeCells count="5">
+    <mergeCell ref="J1:M1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
@@ -3856,85 +5947,68 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="16" width="13.09765625" style="72" customWidth="1"/>
+    <col min="2" max="16" width="13.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
     </row>
     <row r="2" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
     </row>
     <row r="3" spans="1:16" s="9" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -3987,592 +6061,592 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="70">
+      <c r="A6" s="18">
         <v>449266290</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="18">
         <v>10799</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="18">
         <v>10630</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="18">
         <v>10631</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="18">
         <v>10632</v>
       </c>
-      <c r="F6" s="70">
+      <c r="F6" s="18">
         <v>10633</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="18">
         <v>10626</v>
       </c>
-      <c r="H6" s="70">
+      <c r="H6" s="18">
         <v>10628</v>
       </c>
-      <c r="I6" s="70">
+      <c r="I6" s="18">
         <v>10609</v>
       </c>
-      <c r="J6" s="70">
+      <c r="J6" s="18">
         <v>10622</v>
       </c>
-      <c r="K6" s="70">
+      <c r="K6" s="18">
         <v>10624</v>
       </c>
-      <c r="L6" s="70">
+      <c r="L6" s="18">
         <v>10807</v>
       </c>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70">
+      <c r="A7" s="18">
         <v>449266290</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="18">
         <v>10799</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="18">
         <v>10630</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="18">
         <v>10631</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="18">
         <v>10632</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="18">
         <v>10633</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="18">
         <v>10626</v>
       </c>
-      <c r="H7" s="70">
+      <c r="H7" s="18">
         <v>10628</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="18">
         <v>10609</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="18">
         <v>10622</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="18">
         <v>10624</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="18">
         <v>10807</v>
       </c>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
     </row>
     <row r="8" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
     </row>
     <row r="9" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
     </row>
     <row r="10" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
     </row>
     <row r="11" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
     </row>
     <row r="13" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
     </row>
     <row r="14" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
     </row>
     <row r="15" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
     </row>
     <row r="16" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
     </row>
     <row r="17" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
     </row>
     <row r="19" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
     </row>
     <row r="21" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
     </row>
     <row r="22" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
     </row>
     <row r="23" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
     </row>
     <row r="24" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
     </row>
     <row r="25" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
     </row>
     <row r="26" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
     </row>
     <row r="27" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
     </row>
     <row r="28" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="71"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
     </row>
     <row r="29" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
     </row>
     <row r="30" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
     </row>
     <row r="31" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
     </row>
     <row r="32" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
     </row>
     <row r="33" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
     </row>
     <row r="34" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
     </row>
     <row r="35" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4594,85 +6668,68 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="16" width="13.09765625" style="72" customWidth="1"/>
+    <col min="2" max="16" width="13.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
     </row>
     <row r="2" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
     </row>
     <row r="3" spans="1:16" s="9" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4725,572 +6782,572 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="70">
+      <c r="A6" s="18">
         <v>449266290</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="18">
         <v>10799</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="18">
         <v>10630</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="18">
         <v>10631</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="18">
         <v>10632</v>
       </c>
-      <c r="F6" s="70">
+      <c r="F6" s="18">
         <v>10633</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="18">
         <v>10626</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70">
+      <c r="A7" s="18">
         <v>449266290</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="18">
         <v>10626</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="18">
         <v>10628</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="18">
         <v>10609</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="18">
         <v>10622</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="18">
         <v>10624</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="18">
         <v>10807</v>
       </c>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
     </row>
     <row r="8" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
     </row>
     <row r="9" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
     </row>
     <row r="10" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
     </row>
     <row r="11" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
     </row>
     <row r="13" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
     </row>
     <row r="14" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
     </row>
     <row r="15" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
     </row>
     <row r="16" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
     </row>
     <row r="17" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
     </row>
     <row r="19" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
     </row>
     <row r="21" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
     </row>
     <row r="22" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
     </row>
     <row r="23" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
     </row>
     <row r="24" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
     </row>
     <row r="25" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
     </row>
     <row r="26" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
     </row>
     <row r="27" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
     </row>
     <row r="28" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="71"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
     </row>
     <row r="29" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
     </row>
     <row r="30" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
     </row>
     <row r="31" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
     </row>
     <row r="32" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
     </row>
     <row r="33" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
     </row>
     <row r="34" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
     </row>
     <row r="35" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5311,7 +7368,7 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.8984375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="64.59765625" style="74" customWidth="1"/>
+    <col min="2" max="2" width="64.59765625" style="9" customWidth="1"/>
     <col min="3" max="16384" width="8.796875" style="9"/>
   </cols>
   <sheetData>
@@ -5330,572 +7387,569 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="9"/>
-    </row>
     <row r="5" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="70">
+      <c r="B6" s="18">
         <v>449266290</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="70">
+      <c r="B7" s="18">
         <v>449266290</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="73"/>
+      <c r="B8" s="19"/>
     </row>
     <row r="9" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="73"/>
+      <c r="B9" s="19"/>
     </row>
     <row r="10" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="73"/>
+      <c r="B10" s="19"/>
     </row>
     <row r="11" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="73"/>
+      <c r="B11" s="19"/>
     </row>
     <row r="12" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="73"/>
+      <c r="B12" s="19"/>
     </row>
     <row r="13" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="73"/>
+      <c r="B13" s="19"/>
     </row>
     <row r="14" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="73"/>
+      <c r="B14" s="19"/>
     </row>
     <row r="15" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="73"/>
+      <c r="B15" s="19"/>
     </row>
     <row r="16" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="73"/>
+      <c r="B16" s="19"/>
     </row>
     <row r="17" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="73"/>
+      <c r="B17" s="19"/>
     </row>
     <row r="18" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="73"/>
+      <c r="B18" s="19"/>
     </row>
     <row r="19" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="73"/>
+      <c r="B19" s="19"/>
     </row>
     <row r="20" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="73"/>
+      <c r="B20" s="19"/>
     </row>
     <row r="21" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="73"/>
+      <c r="B21" s="19"/>
     </row>
     <row r="22" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="73"/>
+      <c r="B22" s="19"/>
     </row>
     <row r="23" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="73"/>
+      <c r="B23" s="19"/>
     </row>
     <row r="24" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="73"/>
+      <c r="B24" s="19"/>
     </row>
     <row r="25" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="73"/>
+      <c r="B25" s="19"/>
     </row>
     <row r="26" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="73"/>
+      <c r="B26" s="19"/>
     </row>
     <row r="27" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="73"/>
+      <c r="B27" s="19"/>
     </row>
     <row r="28" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="73"/>
+      <c r="B28" s="19"/>
     </row>
     <row r="29" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="73"/>
+      <c r="B29" s="19"/>
     </row>
     <row r="30" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="73"/>
+      <c r="B30" s="19"/>
     </row>
     <row r="31" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="73"/>
+      <c r="B31" s="19"/>
     </row>
     <row r="32" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="73"/>
+      <c r="B32" s="19"/>
     </row>
     <row r="33" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="73"/>
+      <c r="B33" s="19"/>
     </row>
     <row r="34" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="73"/>
+      <c r="B34" s="19"/>
     </row>
     <row r="35" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="73"/>
+      <c r="B35" s="19"/>
     </row>
     <row r="36" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="73"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="73"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="73"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B39" s="73"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B40" s="73"/>
+      <c r="B40" s="19"/>
     </row>
     <row r="41" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B41" s="73"/>
+      <c r="B41" s="19"/>
     </row>
     <row r="42" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B42" s="73"/>
+      <c r="B42" s="19"/>
     </row>
     <row r="43" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B43" s="73"/>
+      <c r="B43" s="19"/>
     </row>
     <row r="44" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B44" s="73"/>
+      <c r="B44" s="19"/>
     </row>
     <row r="45" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B45" s="73"/>
+      <c r="B45" s="19"/>
     </row>
     <row r="46" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B46" s="73"/>
+      <c r="B46" s="19"/>
     </row>
     <row r="47" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B47" s="73"/>
+      <c r="B47" s="19"/>
     </row>
     <row r="48" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B48" s="73"/>
+      <c r="B48" s="19"/>
     </row>
     <row r="49" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B49" s="73"/>
+      <c r="B49" s="19"/>
     </row>
     <row r="50" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B50" s="73"/>
+      <c r="B50" s="19"/>
     </row>
     <row r="51" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B51" s="73"/>
+      <c r="B51" s="19"/>
     </row>
     <row r="52" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B52" s="73"/>
+      <c r="B52" s="19"/>
     </row>
     <row r="53" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B53" s="73"/>
+      <c r="B53" s="19"/>
     </row>
     <row r="54" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B54" s="73"/>
+      <c r="B54" s="19"/>
     </row>
     <row r="55" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B55" s="73"/>
+      <c r="B55" s="19"/>
     </row>
     <row r="56" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B56" s="73"/>
+      <c r="B56" s="19"/>
     </row>
     <row r="57" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B57" s="73"/>
+      <c r="B57" s="19"/>
     </row>
     <row r="58" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B58" s="73"/>
+      <c r="B58" s="19"/>
     </row>
     <row r="59" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B59" s="73"/>
+      <c r="B59" s="19"/>
     </row>
     <row r="60" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B60" s="73"/>
+      <c r="B60" s="19"/>
     </row>
     <row r="61" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B61" s="73"/>
+      <c r="B61" s="19"/>
     </row>
     <row r="62" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B62" s="73"/>
+      <c r="B62" s="19"/>
     </row>
     <row r="63" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B63" s="73"/>
+      <c r="B63" s="19"/>
     </row>
     <row r="64" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B64" s="73"/>
+      <c r="B64" s="19"/>
     </row>
     <row r="65" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B65" s="73"/>
+      <c r="B65" s="19"/>
     </row>
     <row r="66" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B66" s="73"/>
+      <c r="B66" s="19"/>
     </row>
     <row r="67" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B67" s="73"/>
+      <c r="B67" s="19"/>
     </row>
     <row r="68" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B68" s="73"/>
+      <c r="B68" s="19"/>
     </row>
     <row r="69" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B69" s="73"/>
+      <c r="B69" s="19"/>
     </row>
     <row r="70" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B70" s="73"/>
+      <c r="B70" s="19"/>
     </row>
     <row r="71" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B71" s="73"/>
+      <c r="B71" s="19"/>
     </row>
     <row r="72" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B72" s="73"/>
+      <c r="B72" s="19"/>
     </row>
     <row r="73" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B73" s="73"/>
+      <c r="B73" s="19"/>
     </row>
     <row r="74" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B74" s="73"/>
+      <c r="B74" s="19"/>
     </row>
     <row r="75" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B75" s="73"/>
+      <c r="B75" s="19"/>
     </row>
     <row r="76" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B76" s="73"/>
+      <c r="B76" s="19"/>
     </row>
     <row r="77" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B77" s="73"/>
+      <c r="B77" s="19"/>
     </row>
     <row r="78" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B78" s="73"/>
+      <c r="B78" s="19"/>
     </row>
     <row r="79" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B79" s="73"/>
+      <c r="B79" s="19"/>
     </row>
     <row r="80" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B80" s="73"/>
+      <c r="B80" s="19"/>
     </row>
     <row r="81" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B81" s="73"/>
+      <c r="B81" s="19"/>
     </row>
     <row r="82" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B82" s="73"/>
+      <c r="B82" s="19"/>
     </row>
     <row r="83" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B83" s="73"/>
+      <c r="B83" s="19"/>
     </row>
     <row r="84" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B84" s="73"/>
+      <c r="B84" s="19"/>
     </row>
     <row r="85" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B85" s="73"/>
+      <c r="B85" s="19"/>
     </row>
     <row r="86" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B86" s="73"/>
+      <c r="B86" s="19"/>
     </row>
     <row r="87" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B87" s="73"/>
+      <c r="B87" s="19"/>
     </row>
     <row r="88" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B88" s="73"/>
+      <c r="B88" s="19"/>
     </row>
     <row r="89" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B89" s="73"/>
+      <c r="B89" s="19"/>
     </row>
     <row r="90" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B90" s="73"/>
+      <c r="B90" s="19"/>
     </row>
     <row r="91" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B91" s="73"/>
+      <c r="B91" s="19"/>
     </row>
     <row r="92" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B92" s="73"/>
+      <c r="B92" s="19"/>
     </row>
     <row r="93" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B93" s="73"/>
+      <c r="B93" s="19"/>
     </row>
     <row r="94" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B94" s="73"/>
+      <c r="B94" s="19"/>
     </row>
     <row r="95" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B95" s="73"/>
+      <c r="B95" s="19"/>
     </row>
     <row r="96" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B96" s="73"/>
+      <c r="B96" s="19"/>
     </row>
     <row r="97" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B97" s="73"/>
+      <c r="B97" s="19"/>
     </row>
     <row r="98" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B98" s="73"/>
+      <c r="B98" s="19"/>
     </row>
     <row r="99" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B99" s="73"/>
+      <c r="B99" s="19"/>
     </row>
     <row r="100" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B100" s="73"/>
+      <c r="B100" s="19"/>
     </row>
     <row r="101" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B101" s="73"/>
+      <c r="B101" s="19"/>
     </row>
     <row r="102" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B102" s="73"/>
+      <c r="B102" s="19"/>
     </row>
     <row r="103" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B103" s="73"/>
+      <c r="B103" s="19"/>
     </row>
     <row r="104" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B104" s="73"/>
+      <c r="B104" s="19"/>
     </row>
     <row r="105" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B105" s="73"/>
+      <c r="B105" s="19"/>
     </row>
     <row r="106" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B106" s="73"/>
+      <c r="B106" s="19"/>
     </row>
     <row r="107" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B107" s="73"/>
+      <c r="B107" s="19"/>
     </row>
     <row r="108" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B108" s="73"/>
+      <c r="B108" s="19"/>
     </row>
     <row r="109" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B109" s="73"/>
+      <c r="B109" s="19"/>
     </row>
     <row r="110" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B110" s="73"/>
+      <c r="B110" s="19"/>
     </row>
     <row r="111" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B111" s="73"/>
+      <c r="B111" s="19"/>
     </row>
     <row r="112" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B112" s="73"/>
+      <c r="B112" s="19"/>
     </row>
     <row r="113" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B113" s="73"/>
+      <c r="B113" s="19"/>
     </row>
     <row r="114" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B114" s="73"/>
+      <c r="B114" s="19"/>
     </row>
     <row r="115" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B115" s="73"/>
+      <c r="B115" s="19"/>
     </row>
     <row r="116" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B116" s="73"/>
+      <c r="B116" s="19"/>
     </row>
     <row r="117" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B117" s="73"/>
+      <c r="B117" s="19"/>
     </row>
     <row r="118" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B118" s="73"/>
+      <c r="B118" s="19"/>
     </row>
     <row r="119" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B119" s="73"/>
+      <c r="B119" s="19"/>
     </row>
     <row r="120" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B120" s="73"/>
+      <c r="B120" s="19"/>
     </row>
     <row r="121" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B121" s="73"/>
+      <c r="B121" s="19"/>
     </row>
     <row r="122" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B122" s="73"/>
+      <c r="B122" s="19"/>
     </row>
     <row r="123" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B123" s="73"/>
+      <c r="B123" s="19"/>
     </row>
     <row r="124" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B124" s="73"/>
+      <c r="B124" s="19"/>
     </row>
     <row r="125" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B125" s="73"/>
+      <c r="B125" s="19"/>
     </row>
     <row r="126" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B126" s="73"/>
+      <c r="B126" s="19"/>
     </row>
     <row r="127" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B127" s="73"/>
+      <c r="B127" s="19"/>
     </row>
     <row r="128" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B128" s="73"/>
+      <c r="B128" s="19"/>
     </row>
     <row r="129" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B129" s="73"/>
+      <c r="B129" s="19"/>
     </row>
     <row r="130" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B130" s="73"/>
+      <c r="B130" s="19"/>
     </row>
     <row r="131" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B131" s="73"/>
+      <c r="B131" s="19"/>
     </row>
     <row r="132" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B132" s="73"/>
+      <c r="B132" s="19"/>
     </row>
     <row r="133" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B133" s="73"/>
+      <c r="B133" s="19"/>
     </row>
     <row r="134" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B134" s="73"/>
+      <c r="B134" s="19"/>
     </row>
     <row r="135" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B135" s="73"/>
+      <c r="B135" s="19"/>
     </row>
     <row r="136" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B136" s="73"/>
+      <c r="B136" s="19"/>
     </row>
     <row r="137" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B137" s="73"/>
+      <c r="B137" s="19"/>
     </row>
     <row r="138" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B138" s="73"/>
+      <c r="B138" s="19"/>
     </row>
     <row r="139" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B139" s="73"/>
+      <c r="B139" s="19"/>
     </row>
     <row r="140" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B140" s="73"/>
+      <c r="B140" s="19"/>
     </row>
     <row r="141" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B141" s="73"/>
+      <c r="B141" s="19"/>
     </row>
     <row r="142" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B142" s="73"/>
+      <c r="B142" s="19"/>
     </row>
     <row r="143" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B143" s="73"/>
+      <c r="B143" s="19"/>
     </row>
     <row r="144" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B144" s="73"/>
+      <c r="B144" s="19"/>
     </row>
     <row r="145" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B145" s="73"/>
+      <c r="B145" s="19"/>
     </row>
     <row r="146" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B146" s="73"/>
+      <c r="B146" s="19"/>
     </row>
     <row r="147" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B147" s="73"/>
+      <c r="B147" s="19"/>
     </row>
     <row r="148" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B148" s="73"/>
+      <c r="B148" s="19"/>
     </row>
     <row r="149" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B149" s="73"/>
+      <c r="B149" s="19"/>
     </row>
     <row r="150" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B150" s="73"/>
+      <c r="B150" s="19"/>
     </row>
     <row r="151" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B151" s="73"/>
+      <c r="B151" s="19"/>
     </row>
     <row r="152" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B152" s="73"/>
+      <c r="B152" s="19"/>
     </row>
     <row r="153" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B153" s="73"/>
+      <c r="B153" s="19"/>
     </row>
     <row r="154" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B154" s="73"/>
+      <c r="B154" s="19"/>
     </row>
     <row r="155" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B155" s="73"/>
+      <c r="B155" s="19"/>
     </row>
     <row r="156" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B156" s="73"/>
+      <c r="B156" s="19"/>
     </row>
     <row r="157" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B157" s="73"/>
+      <c r="B157" s="19"/>
     </row>
     <row r="158" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B158" s="73"/>
+      <c r="B158" s="19"/>
     </row>
     <row r="159" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B159" s="73"/>
+      <c r="B159" s="19"/>
     </row>
     <row r="160" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B160" s="73"/>
+      <c r="B160" s="19"/>
     </row>
     <row r="161" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B161" s="73"/>
+      <c r="B161" s="19"/>
     </row>
     <row r="162" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B162" s="73"/>
+      <c r="B162" s="19"/>
     </row>
     <row r="163" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B163" s="73"/>
+      <c r="B163" s="19"/>
     </row>
     <row r="164" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B164" s="73"/>
+      <c r="B164" s="19"/>
     </row>
     <row r="165" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B165" s="73"/>
+      <c r="B165" s="19"/>
     </row>
     <row r="166" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B166" s="73"/>
+      <c r="B166" s="19"/>
     </row>
     <row r="167" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B167" s="73"/>
+      <c r="B167" s="19"/>
     </row>
     <row r="168" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B168" s="73"/>
+      <c r="B168" s="19"/>
     </row>
     <row r="169" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B169" s="73"/>
+      <c r="B169" s="19"/>
     </row>
     <row r="170" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B170" s="73"/>
+      <c r="B170" s="19"/>
     </row>
     <row r="171" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B171" s="73"/>
+      <c r="B171" s="19"/>
     </row>
     <row r="172" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B172" s="73"/>
+      <c r="B172" s="19"/>
     </row>
     <row r="173" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B173" s="73"/>
+      <c r="B173" s="19"/>
     </row>
     <row r="174" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B174" s="73"/>
+      <c r="B174" s="19"/>
     </row>
     <row r="175" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B175" s="73"/>
+      <c r="B175" s="19"/>
     </row>
     <row r="176" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B176" s="73"/>
+      <c r="B176" s="19"/>
     </row>
     <row r="177" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B177" s="73"/>
+      <c r="B177" s="19"/>
     </row>
     <row r="178" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B178" s="73"/>
+      <c r="B178" s="19"/>
     </row>
     <row r="179" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B179" s="73"/>
+      <c r="B179" s="19"/>
     </row>
     <row r="180" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B180" s="73"/>
+      <c r="B180" s="19"/>
     </row>
     <row r="181" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B181" s="73"/>
+      <c r="B181" s="19"/>
     </row>
     <row r="182" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B182" s="73"/>
+      <c r="B182" s="19"/>
     </row>
     <row r="183" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B183" s="73"/>
+      <c r="B183" s="19"/>
     </row>
     <row r="184" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B184" s="73"/>
+      <c r="B184" s="19"/>
     </row>
     <row r="185" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B185" s="73"/>
+      <c r="B185" s="19"/>
     </row>
     <row r="186" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B186" s="73"/>
+      <c r="B186" s="19"/>
     </row>
     <row r="187" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B187" s="73"/>
+      <c r="B187" s="19"/>
     </row>
     <row r="188" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B188" s="73"/>
+      <c r="B188" s="19"/>
     </row>
     <row r="189" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B189" s="73"/>
+      <c r="B189" s="19"/>
     </row>
     <row r="190" spans="2:2" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="B190" s="73"/>
+      <c r="B190" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5936,20 +7990,20 @@
       </c>
     </row>
     <row r="6" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="70">
+      <c r="B6" s="18">
         <v>449266290</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="70">
+      <c r="B7" s="18">
         <v>449266290</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="73"/>
+      <c r="B8" s="19"/>
     </row>
     <row r="9" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="73"/>
+      <c r="B9" s="19"/>
     </row>
     <row r="10" spans="2:2" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="19"/>
@@ -6508,85 +8562,68 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="16" width="13.09765625" style="72" customWidth="1"/>
+    <col min="2" max="16" width="13.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
     </row>
     <row r="2" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
     </row>
     <row r="3" spans="1:16" s="9" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4"/>
-      <c r="P4"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -6639,560 +8676,560 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="70">
+      <c r="A6" s="18">
         <v>449266290</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="18">
         <v>10799</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="18">
         <v>-10630</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="18">
         <v>10631</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70">
+      <c r="A7" s="18">
         <v>449266290</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="18">
         <v>10799</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="18">
         <v>10630</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="18">
         <v>-10631</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
     </row>
     <row r="8" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
     </row>
     <row r="9" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
     </row>
     <row r="10" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
     </row>
     <row r="11" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
     </row>
     <row r="12" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
     </row>
     <row r="13" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
     </row>
     <row r="14" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
     </row>
     <row r="15" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
     </row>
     <row r="16" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
     </row>
     <row r="17" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
     </row>
     <row r="18" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
     </row>
     <row r="19" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
     </row>
     <row r="21" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
     </row>
     <row r="22" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
     </row>
     <row r="23" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
     </row>
     <row r="24" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
     </row>
     <row r="25" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
     </row>
     <row r="26" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
     </row>
     <row r="27" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
     </row>
     <row r="28" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="71"/>
-      <c r="K28" s="71"/>
-      <c r="L28" s="71"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="71"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="71"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
     </row>
     <row r="29" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
     </row>
     <row r="30" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
     </row>
     <row r="31" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
     </row>
     <row r="32" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
     </row>
     <row r="33" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
     </row>
     <row r="34" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
     </row>
     <row r="35" spans="1:16" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7230,34 +9267,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="2" spans="1:6" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="1:6" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F4"/>
@@ -7579,37 +9616,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -7982,22 +10019,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="41"/>
     </row>
     <row r="2" spans="1:2" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="28"/>
+      <c r="B2" s="41"/>
     </row>
     <row r="3" spans="1:2" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="28"/>
+      <c r="B3" s="41"/>
     </row>
     <row r="5" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -9420,7 +11457,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>48</v>
       </c>
     </row>
@@ -9430,7 +11467,7 @@
       </c>
     </row>
     <row r="3" spans="1:1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10019,17 +12056,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="9" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="65" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="9" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="64" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="9" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="64" t="s">
         <v>52</v>
       </c>
     </row>

--- a/RayatAuto-data-template.xlsx
+++ b/RayatAuto-data-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\البرامج المطورة\من الفايز - تحت المراجعة\POWERAUTO\RayatAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA3F476-C4F9-46FA-A968-3BA68EBF92C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4104DABE-3452-406F-AB3E-C311F9E4AAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="893" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,9 +1215,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0000000"/>
     <numFmt numFmtId="165" formatCode="0000000000"/>
-    <numFmt numFmtId="168" formatCode="0000;\-0000;0"/>
+    <numFmt numFmtId="166" formatCode="0000;\-0000;0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1378,6 +1378,13 @@
       <sz val="11"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1586,7 +1593,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1674,120 +1681,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
@@ -1806,6 +1700,105 @@
     <xf numFmtId="49" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1815,13 +1808,30 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
@@ -2156,36 +2166,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="1:8" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2198,598 +2208,645 @@
       <c r="H4" s="5"/>
     </row>
     <row r="6" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
     </row>
     <row r="7" spans="1:8" s="9" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" s="9" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
     </row>
     <row r="11" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
     </row>
     <row r="12" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
     </row>
     <row r="13" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
     </row>
     <row r="14" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
     </row>
     <row r="15" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
     </row>
     <row r="16" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
     </row>
     <row r="21" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
     </row>
     <row r="23" spans="1:8" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
     </row>
     <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="58" t="s">
+      <c r="A25" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
     </row>
     <row r="26" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="56" t="s">
+      <c r="B26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="57"/>
-      <c r="F26" s="56" t="s">
+      <c r="E26" s="85"/>
+      <c r="F26" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="85"/>
     </row>
     <row r="27" spans="1:8" s="25" customFormat="1" ht="5.4" x14ac:dyDescent="0.15"/>
     <row r="28" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
     </row>
     <row r="29" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="62"/>
+      <c r="B29" s="55"/>
       <c r="C29" s="26" t="str">
         <f t="shared" ref="C29:C39" si="0">HYPERLINK("#'" &amp; A29 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
-      <c r="D29" s="42" t="s">
+      <c r="D29" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="42" t="s">
+      <c r="E29" s="59"/>
+      <c r="F29" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="49"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="60"/>
     </row>
     <row r="30" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="36"/>
+      <c r="B30" s="42"/>
       <c r="C30" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="36" t="s">
+      <c r="E30" s="49"/>
+      <c r="F30" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="45"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="50"/>
     </row>
     <row r="31" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="31"/>
+      <c r="B31" s="51"/>
       <c r="C31" s="28" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="33" t="s">
+      <c r="E31" s="49"/>
+      <c r="F31" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="32"/>
-      <c r="H31" s="45"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="50"/>
     </row>
     <row r="32" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="36"/>
+      <c r="B32" s="42"/>
       <c r="C32" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="32"/>
-      <c r="F32" s="36" t="s">
+      <c r="E32" s="49"/>
+      <c r="F32" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="45"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="50"/>
     </row>
     <row r="33" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="31"/>
+      <c r="B33" s="51"/>
       <c r="C33" s="28" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="33" t="s">
+      <c r="E33" s="49"/>
+      <c r="F33" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="45"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="50"/>
     </row>
     <row r="34" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="36"/>
+      <c r="B34" s="42"/>
       <c r="C34" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="36" t="s">
+      <c r="E34" s="49"/>
+      <c r="F34" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="45"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="50"/>
     </row>
     <row r="35" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="31"/>
+      <c r="B35" s="51"/>
       <c r="C35" s="28" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="32"/>
-      <c r="F35" s="33" t="s">
+      <c r="E35" s="49"/>
+      <c r="F35" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G35" s="32"/>
-      <c r="H35" s="45"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="50"/>
     </row>
     <row r="36" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="36"/>
+      <c r="B36" s="42"/>
       <c r="C36" s="27" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="32"/>
-      <c r="F36" s="36" t="s">
+      <c r="E36" s="49"/>
+      <c r="F36" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G36" s="32"/>
-      <c r="H36" s="45"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="50"/>
     </row>
     <row r="37" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="31"/>
+      <c r="B37" s="51"/>
       <c r="C37" s="28" t="str">
         <f t="shared" ref="C37:C38" si="1">HYPERLINK("#'" &amp; A37 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="32"/>
-      <c r="F37" s="33" t="s">
+      <c r="E37" s="49"/>
+      <c r="F37" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G37" s="32"/>
-      <c r="H37" s="45"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="50"/>
     </row>
     <row r="38" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="28" t="str">
+      <c r="B38" s="81"/>
+      <c r="C38" s="27" t="str">
         <f t="shared" si="1"/>
         <v>انتقل</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="36" t="s">
+      <c r="E38" s="49"/>
+      <c r="F38" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G38" s="32"/>
-      <c r="H38" s="45"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="50"/>
     </row>
     <row r="39" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="63"/>
+      <c r="B39" s="41"/>
       <c r="C39" s="29" t="str">
         <f t="shared" si="0"/>
         <v>انتقل</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="33" t="s">
+      <c r="E39" s="53"/>
+      <c r="F39" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G39" s="39"/>
-      <c r="H39" s="61"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="54"/>
     </row>
     <row r="40" spans="1:8" s="25" customFormat="1" ht="5.4" x14ac:dyDescent="0.15"/>
     <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="35"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="69"/>
     </row>
     <row r="42" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="51"/>
       <c r="C42" s="28" t="str">
         <f t="shared" ref="C42:C46" si="2">HYPERLINK("#'" &amp; A42 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="32"/>
-      <c r="F42" s="33" t="s">
+      <c r="E42" s="49"/>
+      <c r="F42" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
     </row>
     <row r="43" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="36"/>
+      <c r="B43" s="42"/>
       <c r="C43" s="27" t="str">
         <f t="shared" ref="C43:C44" si="3">HYPERLINK("#'" &amp; A43 &amp; "'!A1", "انتقل")</f>
         <v>انتقل</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="36" t="s">
+      <c r="E43" s="49"/>
+      <c r="F43" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
     </row>
     <row r="44" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="31"/>
+      <c r="B44" s="51"/>
       <c r="C44" s="28" t="str">
         <f t="shared" si="3"/>
         <v>انتقل</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="32"/>
-      <c r="F44" s="33" t="s">
+      <c r="E44" s="49"/>
+      <c r="F44" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
     </row>
     <row r="45" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="36"/>
+      <c r="B45" s="42"/>
       <c r="C45" s="27" t="str">
         <f t="shared" si="2"/>
         <v>انتقل</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="32"/>
-      <c r="F45" s="36" t="s">
+      <c r="E45" s="49"/>
+      <c r="F45" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
     </row>
     <row r="46" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="31"/>
+      <c r="B46" s="51"/>
       <c r="C46" s="28" t="str">
         <f t="shared" si="2"/>
         <v>انتقل</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="33" t="s">
+      <c r="E46" s="49"/>
+      <c r="F46" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="49"/>
     </row>
     <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="40" t="s">
+      <c r="A48" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="41"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="46"/>
     </row>
     <row r="49" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="41"/>
-      <c r="B49" s="41"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
     </row>
     <row r="50" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="37" t="s">
+      <c r="A50" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
+      <c r="B50" s="65"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
     </row>
     <row r="52" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="59" t="s">
+      <c r="A52" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A48:H49"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A7:H8"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A13:H13"/>
@@ -2806,58 +2863,11 @@
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A7:H8"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A48:H49"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A50" r:id="rId1" display="🔗 صفحة المشروع (مرجع دائم): https://myalsh2030.github.io/rayatauto-firefox/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2882,22 +2892,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="46"/>
     </row>
     <row r="2" spans="1:2" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="41"/>
+      <c r="B2" s="46"/>
     </row>
     <row r="3" spans="1:2" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="41"/>
+      <c r="B3" s="46"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
@@ -3712,91 +3722,91 @@
   <dimension ref="A1:M98"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14" style="71" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" style="71" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" style="71" customWidth="1"/>
-    <col min="4" max="4" width="14.8984375" style="84" customWidth="1"/>
-    <col min="5" max="5" width="16" style="71" customWidth="1"/>
-    <col min="6" max="6" width="3.296875" style="71" customWidth="1"/>
-    <col min="7" max="7" width="40" style="71" customWidth="1"/>
-    <col min="8" max="8" width="18.5" style="71" customWidth="1"/>
-    <col min="9" max="9" width="3.296875" style="71" customWidth="1"/>
-    <col min="10" max="10" width="11" style="71" customWidth="1"/>
-    <col min="11" max="11" width="34" style="71" customWidth="1"/>
-    <col min="12" max="12" width="12" style="71" customWidth="1"/>
-    <col min="13" max="13" width="38" style="71" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="71"/>
+    <col min="1" max="1" width="14" style="31" customWidth="1"/>
+    <col min="2" max="2" width="18.69921875" style="31" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="31" customWidth="1"/>
+    <col min="4" max="4" width="14.8984375" style="40" customWidth="1"/>
+    <col min="5" max="5" width="16" style="31" customWidth="1"/>
+    <col min="6" max="6" width="3.296875" style="31" customWidth="1"/>
+    <col min="7" max="7" width="40" style="31" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="31" customWidth="1"/>
+    <col min="9" max="9" width="3.296875" style="31" customWidth="1"/>
+    <col min="10" max="10" width="11" style="31" customWidth="1"/>
+    <col min="11" max="11" width="34" style="31" customWidth="1"/>
+    <col min="12" max="12" width="12" style="31" customWidth="1"/>
+    <col min="13" max="13" width="38" style="31" customWidth="1"/>
+    <col min="14" max="16384" width="8.796875" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="J1" s="79" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="J1" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="81"/>
-    </row>
-    <row r="2" spans="1:13" s="73" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="64" t="s">
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="75"/>
+    </row>
+    <row r="2" spans="1:13" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="J2" s="74" t="s">
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="J2" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="74" t="s">
+      <c r="L2" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="M2" s="74" t="s">
+      <c r="M2" s="33" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="73" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:13" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="J3" s="75" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="J3" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K3" s="76" t="s">
+      <c r="K3" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="L3" s="75" t="s">
+      <c r="L3" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="M3" s="76" t="s">
+      <c r="M3" s="35" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="D4" s="71"/>
-      <c r="J4" s="77" t="s">
+      <c r="D4" s="31"/>
+      <c r="J4" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="K4" s="78" t="s">
+      <c r="K4" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="M4" s="78" t="s">
+      <c r="M4" s="37" t="s">
         <v>161</v>
       </c>
     </row>
@@ -3816,16 +3826,16 @@
       <c r="E5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K5" s="76" t="s">
+      <c r="K5" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="L5" s="75" t="s">
+      <c r="L5" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="M5" s="76" t="s">
+      <c r="M5" s="35" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3839,7 +3849,7 @@
       <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6" s="82">
+      <c r="D6" s="38">
         <v>209</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -3848,19 +3858,19 @@
       <c r="G6" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="77" t="s">
+      <c r="J6" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="K6" s="78" t="s">
+      <c r="K6" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="L6" s="77" t="s">
+      <c r="L6" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="M6" s="78" t="s">
+      <c r="M6" s="37" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3874,7 +3884,7 @@
       <c r="C7" s="7">
         <v>401</v>
       </c>
-      <c r="D7" s="82">
+      <c r="D7" s="38">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -3883,17 +3893,17 @@
       <c r="G7" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="69"/>
-      <c r="J7" s="75" t="s">
+      <c r="H7" s="80"/>
+      <c r="J7" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K7" s="76" t="s">
+      <c r="K7" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="L7" s="75" t="s">
+      <c r="L7" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="M7" s="76" t="s">
+      <c r="M7" s="35" t="s">
         <v>167</v>
       </c>
     </row>
@@ -3901,18 +3911,18 @@
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="83"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="8"/>
-      <c r="J8" s="77" t="s">
+      <c r="J8" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="L8" s="77" t="s">
+      <c r="L8" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="M8" s="78" t="s">
+      <c r="M8" s="37" t="s">
         <v>169</v>
       </c>
     </row>
@@ -3920,18 +3930,18 @@
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="83"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="8"/>
-      <c r="J9" s="75" t="s">
+      <c r="J9" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K9" s="76" t="s">
+      <c r="K9" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="L9" s="75" t="s">
+      <c r="L9" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="76" t="s">
+      <c r="M9" s="35" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3939,18 +3949,18 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="83"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="8"/>
-      <c r="J10" s="77" t="s">
+      <c r="J10" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="K10" s="78" t="s">
+      <c r="K10" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="M10" s="78" t="s">
+      <c r="M10" s="37" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3958,18 +3968,18 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="83"/>
+      <c r="D11" s="39"/>
       <c r="E11" s="8"/>
-      <c r="J11" s="75" t="s">
+      <c r="J11" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K11" s="76" t="s">
+      <c r="K11" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="L11" s="75" t="s">
+      <c r="L11" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="76" t="s">
+      <c r="M11" s="35" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3977,18 +3987,18 @@
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="83"/>
+      <c r="D12" s="39"/>
       <c r="E12" s="8"/>
-      <c r="J12" s="77" t="s">
+      <c r="J12" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="K12" s="78" t="s">
+      <c r="K12" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="L12" s="77" t="s">
+      <c r="L12" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="M12" s="78" t="s">
+      <c r="M12" s="37" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3996,18 +4006,18 @@
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="83"/>
+      <c r="D13" s="39"/>
       <c r="E13" s="8"/>
-      <c r="J13" s="75" t="s">
+      <c r="J13" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K13" s="76" t="s">
+      <c r="K13" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="L13" s="75" t="s">
+      <c r="L13" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="M13" s="76" t="s">
+      <c r="M13" s="35" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4015,18 +4025,18 @@
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="83"/>
+      <c r="D14" s="39"/>
       <c r="E14" s="8"/>
-      <c r="J14" s="77" t="s">
+      <c r="J14" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K14" s="78" t="s">
+      <c r="K14" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L14" s="77" t="s">
+      <c r="L14" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="M14" s="78" t="s">
+      <c r="M14" s="37" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4034,18 +4044,18 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="83"/>
+      <c r="D15" s="39"/>
       <c r="E15" s="8"/>
-      <c r="J15" s="75" t="s">
+      <c r="J15" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K15" s="76" t="s">
+      <c r="K15" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L15" s="75" t="s">
+      <c r="L15" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="M15" s="76" t="s">
+      <c r="M15" s="35" t="s">
         <v>185</v>
       </c>
     </row>
@@ -4053,18 +4063,18 @@
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="83"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="8"/>
-      <c r="J16" s="77" t="s">
+      <c r="J16" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="78" t="s">
+      <c r="K16" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="77" t="s">
+      <c r="L16" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="M16" s="78" t="s">
+      <c r="M16" s="37" t="s">
         <v>187</v>
       </c>
     </row>
@@ -4072,18 +4082,18 @@
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="83"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="8"/>
-      <c r="J17" s="75" t="s">
+      <c r="J17" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K17" s="76" t="s">
+      <c r="K17" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L17" s="75" t="s">
+      <c r="L17" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="M17" s="76" t="s">
+      <c r="M17" s="35" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4091,18 +4101,18 @@
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="83"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="8"/>
-      <c r="J18" s="77" t="s">
+      <c r="J18" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K18" s="78" t="s">
+      <c r="K18" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L18" s="77" t="s">
+      <c r="L18" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="M18" s="78" t="s">
+      <c r="M18" s="37" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4110,18 +4120,18 @@
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="83"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="8"/>
-      <c r="J19" s="75" t="s">
+      <c r="J19" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K19" s="76" t="s">
+      <c r="K19" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L19" s="75" t="s">
+      <c r="L19" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="M19" s="76" t="s">
+      <c r="M19" s="35" t="s">
         <v>193</v>
       </c>
     </row>
@@ -4129,18 +4139,18 @@
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="83"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="8"/>
-      <c r="J20" s="77" t="s">
+      <c r="J20" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K20" s="78" t="s">
+      <c r="K20" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L20" s="77" t="s">
+      <c r="L20" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="M20" s="78" t="s">
+      <c r="M20" s="37" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4148,18 +4158,18 @@
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="83"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="8"/>
-      <c r="J21" s="75" t="s">
+      <c r="J21" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K21" s="76" t="s">
+      <c r="K21" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L21" s="75" t="s">
+      <c r="L21" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="M21" s="76" t="s">
+      <c r="M21" s="35" t="s">
         <v>197</v>
       </c>
     </row>
@@ -4167,18 +4177,18 @@
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="83"/>
+      <c r="D22" s="39"/>
       <c r="E22" s="8"/>
-      <c r="J22" s="77" t="s">
+      <c r="J22" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K22" s="78" t="s">
+      <c r="K22" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L22" s="77" t="s">
+      <c r="L22" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="M22" s="78" t="s">
+      <c r="M22" s="37" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4186,18 +4196,18 @@
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="83"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="8"/>
-      <c r="J23" s="75" t="s">
+      <c r="J23" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K23" s="76" t="s">
+      <c r="K23" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L23" s="75" t="s">
+      <c r="L23" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="M23" s="76" t="s">
+      <c r="M23" s="35" t="s">
         <v>201</v>
       </c>
     </row>
@@ -4205,18 +4215,18 @@
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="83"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="8"/>
-      <c r="J24" s="77" t="s">
+      <c r="J24" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K24" s="78" t="s">
+      <c r="K24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="77" t="s">
+      <c r="L24" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="M24" s="78" t="s">
+      <c r="M24" s="37" t="s">
         <v>203</v>
       </c>
     </row>
@@ -4224,18 +4234,18 @@
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="83"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="8"/>
-      <c r="J25" s="75" t="s">
+      <c r="J25" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K25" s="76" t="s">
+      <c r="K25" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="75" t="s">
+      <c r="L25" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="M25" s="76" t="s">
+      <c r="M25" s="35" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4243,18 +4253,18 @@
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="83"/>
+      <c r="D26" s="39"/>
       <c r="E26" s="8"/>
-      <c r="J26" s="77" t="s">
+      <c r="J26" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K26" s="78" t="s">
+      <c r="K26" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="77" t="s">
+      <c r="L26" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="M26" s="78" t="s">
+      <c r="M26" s="37" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4262,18 +4272,18 @@
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="83"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="8"/>
-      <c r="J27" s="75" t="s">
+      <c r="J27" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K27" s="76" t="s">
+      <c r="K27" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L27" s="75" t="s">
+      <c r="L27" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="M27" s="76" t="s">
+      <c r="M27" s="35" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4281,18 +4291,18 @@
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="83"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="8"/>
-      <c r="J28" s="77" t="s">
+      <c r="J28" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K28" s="78" t="s">
+      <c r="K28" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="77" t="s">
+      <c r="L28" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="M28" s="78" t="s">
+      <c r="M28" s="37" t="s">
         <v>211</v>
       </c>
     </row>
@@ -4300,18 +4310,18 @@
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="83"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="8"/>
-      <c r="J29" s="75" t="s">
+      <c r="J29" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="K29" s="76" t="s">
+      <c r="K29" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L29" s="75" t="s">
+      <c r="L29" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="M29" s="76" t="s">
+      <c r="M29" s="35" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4319,18 +4329,18 @@
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="83"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="8"/>
-      <c r="J30" s="77" t="s">
+      <c r="J30" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="K30" s="78" t="s">
+      <c r="K30" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="L30" s="77" t="s">
+      <c r="L30" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="M30" s="78" t="s">
+      <c r="M30" s="37" t="s">
         <v>215</v>
       </c>
     </row>
@@ -4338,18 +4348,18 @@
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="83"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="8"/>
-      <c r="J31" s="75" t="s">
+      <c r="J31" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="K31" s="76" t="s">
+      <c r="K31" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="L31" s="75" t="s">
+      <c r="L31" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="M31" s="76" t="s">
+      <c r="M31" s="35" t="s">
         <v>219</v>
       </c>
     </row>
@@ -4357,18 +4367,18 @@
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="83"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="8"/>
-      <c r="J32" s="77" t="s">
+      <c r="J32" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K32" s="78" t="s">
+      <c r="K32" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="L32" s="77" t="s">
+      <c r="L32" s="36" t="s">
         <v>220</v>
       </c>
-      <c r="M32" s="78" t="s">
+      <c r="M32" s="37" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4376,18 +4386,18 @@
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="83"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="8"/>
-      <c r="J33" s="75" t="s">
+      <c r="J33" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="K33" s="76" t="s">
+      <c r="K33" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="L33" s="75" t="s">
+      <c r="L33" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="M33" s="76" t="s">
+      <c r="M33" s="35" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4395,18 +4405,18 @@
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="83"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="8"/>
-      <c r="J34" s="77" t="s">
+      <c r="J34" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K34" s="78" t="s">
+      <c r="K34" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="L34" s="77" t="s">
+      <c r="L34" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="M34" s="78" t="s">
+      <c r="M34" s="37" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4414,18 +4424,18 @@
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="83"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="8"/>
-      <c r="J35" s="75" t="s">
+      <c r="J35" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="K35" s="76" t="s">
+      <c r="K35" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="L35" s="75" t="s">
+      <c r="L35" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="M35" s="76" t="s">
+      <c r="M35" s="35" t="s">
         <v>227</v>
       </c>
     </row>
@@ -4433,18 +4443,18 @@
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="83"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="8"/>
-      <c r="J36" s="77" t="s">
+      <c r="J36" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K36" s="78" t="s">
+      <c r="K36" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="L36" s="77" t="s">
+      <c r="L36" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="M36" s="78" t="s">
+      <c r="M36" s="37" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4452,873 +4462,873 @@
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="83"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="8"/>
-      <c r="J37" s="75" t="s">
+      <c r="J37" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="K37" s="76" t="s">
+      <c r="K37" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="L37" s="75" t="s">
+      <c r="L37" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="M37" s="76" t="s">
+      <c r="M37" s="35" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J38" s="77" t="s">
+      <c r="J38" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="K38" s="78" t="s">
+      <c r="K38" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="L38" s="77" t="s">
+      <c r="L38" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="M38" s="78" t="s">
+      <c r="M38" s="37" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="10"/>
-      <c r="J39" s="75" t="s">
+      <c r="J39" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="K39" s="76" t="s">
+      <c r="K39" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="L39" s="75" t="s">
+      <c r="L39" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="M39" s="76" t="s">
+      <c r="M39" s="35" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J40" s="77" t="s">
+      <c r="J40" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="K40" s="78" t="s">
+      <c r="K40" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="L40" s="77" t="s">
+      <c r="L40" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="M40" s="78" t="s">
+      <c r="M40" s="37" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J41" s="75" t="s">
+      <c r="J41" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="K41" s="76" t="s">
+      <c r="K41" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="L41" s="75" t="s">
+      <c r="L41" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="M41" s="76" t="s">
+      <c r="M41" s="35" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J42" s="77" t="s">
+      <c r="J42" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="K42" s="78" t="s">
+      <c r="K42" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="L42" s="77" t="s">
+      <c r="L42" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="M42" s="78" t="s">
+      <c r="M42" s="37" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J43" s="75" t="s">
+      <c r="J43" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="K43" s="76" t="s">
+      <c r="K43" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="L43" s="75" t="s">
+      <c r="L43" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="M43" s="76" t="s">
+      <c r="M43" s="35" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J44" s="77" t="s">
+      <c r="J44" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="K44" s="78" t="s">
+      <c r="K44" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="L44" s="77" t="s">
+      <c r="L44" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="M44" s="78" t="s">
+      <c r="M44" s="37" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J45" s="75" t="s">
+      <c r="J45" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="K45" s="76" t="s">
+      <c r="K45" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="L45" s="75" t="s">
+      <c r="L45" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="M45" s="76" t="s">
+      <c r="M45" s="35" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J46" s="77" t="s">
+      <c r="J46" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="K46" s="78" t="s">
+      <c r="K46" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="L46" s="77" t="s">
+      <c r="L46" s="36" t="s">
         <v>250</v>
       </c>
-      <c r="M46" s="78" t="s">
+      <c r="M46" s="37" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J47" s="75" t="s">
+      <c r="J47" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="K47" s="76" t="s">
+      <c r="K47" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="L47" s="75" t="s">
+      <c r="L47" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="M47" s="76" t="s">
+      <c r="M47" s="35" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="J48" s="77" t="s">
+      <c r="J48" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="K48" s="78" t="s">
+      <c r="K48" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="L48" s="77" t="s">
+      <c r="L48" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="M48" s="78" t="s">
+      <c r="M48" s="37" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="49" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J49" s="75" t="s">
+      <c r="J49" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="K49" s="76" t="s">
+      <c r="K49" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="L49" s="75" t="s">
+      <c r="L49" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="M49" s="76" t="s">
+      <c r="M49" s="35" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="50" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J50" s="77" t="s">
+      <c r="J50" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="K50" s="78" t="s">
+      <c r="K50" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="L50" s="77" t="s">
+      <c r="L50" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="M50" s="78" t="s">
+      <c r="M50" s="37" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="51" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J51" s="75" t="s">
+      <c r="J51" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="K51" s="76" t="s">
+      <c r="K51" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="L51" s="75" t="s">
+      <c r="L51" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="M51" s="76" t="s">
+      <c r="M51" s="35" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="52" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J52" s="77" t="s">
+      <c r="J52" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="K52" s="78" t="s">
+      <c r="K52" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="L52" s="77" t="s">
+      <c r="L52" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="M52" s="78" t="s">
+      <c r="M52" s="37" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="53" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J53" s="75" t="s">
+      <c r="J53" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="K53" s="76" t="s">
+      <c r="K53" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="L53" s="75" t="s">
+      <c r="L53" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="M53" s="76" t="s">
+      <c r="M53" s="35" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="54" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J54" s="77" t="s">
+      <c r="J54" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="K54" s="78" t="s">
+      <c r="K54" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="L54" s="77" t="s">
+      <c r="L54" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="M54" s="78" t="s">
+      <c r="M54" s="37" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="55" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J55" s="75" t="s">
+      <c r="J55" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="K55" s="76" t="s">
+      <c r="K55" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="L55" s="75" t="s">
+      <c r="L55" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="M55" s="76" t="s">
+      <c r="M55" s="35" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="56" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J56" s="77" t="s">
+      <c r="J56" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="K56" s="78" t="s">
+      <c r="K56" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="L56" s="77" t="s">
+      <c r="L56" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="M56" s="78" t="s">
+      <c r="M56" s="37" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="57" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J57" s="75" t="s">
+      <c r="J57" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="K57" s="76" t="s">
+      <c r="K57" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="L57" s="75" t="s">
+      <c r="L57" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="M57" s="76" t="s">
+      <c r="M57" s="35" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="58" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J58" s="77" t="s">
+      <c r="J58" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="K58" s="78" t="s">
+      <c r="K58" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="L58" s="77" t="s">
+      <c r="L58" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="M58" s="78" t="s">
+      <c r="M58" s="37" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="59" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J59" s="75" t="s">
+      <c r="J59" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="K59" s="76" t="s">
+      <c r="K59" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="L59" s="75" t="s">
+      <c r="L59" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="M59" s="76" t="s">
+      <c r="M59" s="35" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="60" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J60" s="77" t="s">
+      <c r="J60" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="K60" s="78" t="s">
+      <c r="K60" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="L60" s="77" t="s">
+      <c r="L60" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="M60" s="78" t="s">
+      <c r="M60" s="37" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="61" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J61" s="75" t="s">
+      <c r="J61" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="K61" s="76" t="s">
+      <c r="K61" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="L61" s="75" t="s">
+      <c r="L61" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="M61" s="76" t="s">
+      <c r="M61" s="35" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="62" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J62" s="77" t="s">
+      <c r="J62" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="K62" s="78" t="s">
+      <c r="K62" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="L62" s="77" t="s">
+      <c r="L62" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="M62" s="78" t="s">
+      <c r="M62" s="37" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="63" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J63" s="75" t="s">
+      <c r="J63" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="K63" s="76" t="s">
+      <c r="K63" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="L63" s="75" t="s">
+      <c r="L63" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="M63" s="76" t="s">
+      <c r="M63" s="35" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="64" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J64" s="77" t="s">
+      <c r="J64" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="K64" s="78" t="s">
+      <c r="K64" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="L64" s="77" t="s">
+      <c r="L64" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="M64" s="78" t="s">
+      <c r="M64" s="37" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="65" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J65" s="75" t="s">
+      <c r="J65" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="K65" s="76" t="s">
+      <c r="K65" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="L65" s="75" t="s">
+      <c r="L65" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="M65" s="76" t="s">
+      <c r="M65" s="35" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="66" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J66" s="77" t="s">
+      <c r="J66" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="K66" s="78" t="s">
+      <c r="K66" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="L66" s="77" t="s">
+      <c r="L66" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="M66" s="78" t="s">
+      <c r="M66" s="37" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="67" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J67" s="75" t="s">
+      <c r="J67" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="K67" s="76" t="s">
+      <c r="K67" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="L67" s="75" t="s">
+      <c r="L67" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="M67" s="76" t="s">
+      <c r="M67" s="35" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="68" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J68" s="77" t="s">
+      <c r="J68" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="K68" s="78" t="s">
+      <c r="K68" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="L68" s="77" t="s">
+      <c r="L68" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="M68" s="78" t="s">
+      <c r="M68" s="37" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="69" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J69" s="75" t="s">
+      <c r="J69" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="K69" s="76" t="s">
+      <c r="K69" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="L69" s="75" t="s">
+      <c r="L69" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="M69" s="76" t="s">
+      <c r="M69" s="35" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="70" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J70" s="77" t="s">
+      <c r="J70" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="K70" s="78" t="s">
+      <c r="K70" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="L70" s="77" t="s">
+      <c r="L70" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="M70" s="78" t="s">
+      <c r="M70" s="37" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="71" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J71" s="75" t="s">
+      <c r="J71" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="K71" s="76" t="s">
+      <c r="K71" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="L71" s="75" t="s">
+      <c r="L71" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="M71" s="76" t="s">
+      <c r="M71" s="35" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="72" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J72" s="77" t="s">
+      <c r="J72" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="K72" s="78" t="s">
+      <c r="K72" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="L72" s="77" t="s">
+      <c r="L72" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="M72" s="78" t="s">
+      <c r="M72" s="37" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="73" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J73" s="75" t="s">
+      <c r="J73" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="K73" s="76" t="s">
+      <c r="K73" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="L73" s="75" t="s">
+      <c r="L73" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="M73" s="76" t="s">
+      <c r="M73" s="35" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="74" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J74" s="77" t="s">
+      <c r="J74" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="K74" s="78" t="s">
+      <c r="K74" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="L74" s="77" t="s">
+      <c r="L74" s="36" t="s">
         <v>318</v>
       </c>
-      <c r="M74" s="78" t="s">
+      <c r="M74" s="37" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="75" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J75" s="75" t="s">
+      <c r="J75" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="K75" s="76" t="s">
+      <c r="K75" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="L75" s="75" t="s">
+      <c r="L75" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="M75" s="76" t="s">
+      <c r="M75" s="35" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="76" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J76" s="77" t="s">
+      <c r="J76" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="K76" s="78" t="s">
+      <c r="K76" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="L76" s="77" t="s">
+      <c r="L76" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="M76" s="78" t="s">
+      <c r="M76" s="37" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="77" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J77" s="75" t="s">
+      <c r="J77" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="K77" s="76" t="s">
+      <c r="K77" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="L77" s="75" t="s">
+      <c r="L77" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="M77" s="76" t="s">
+      <c r="M77" s="35" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="78" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J78" s="77" t="s">
+      <c r="J78" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="K78" s="78" t="s">
+      <c r="K78" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="L78" s="77" t="s">
+      <c r="L78" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="M78" s="78" t="s">
+      <c r="M78" s="37" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="79" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J79" s="75" t="s">
+      <c r="J79" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="K79" s="76" t="s">
+      <c r="K79" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="L79" s="75" t="s">
+      <c r="L79" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="M79" s="76" t="s">
+      <c r="M79" s="35" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="80" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J80" s="77" t="s">
+      <c r="J80" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="K80" s="78" t="s">
+      <c r="K80" s="37" t="s">
         <v>329</v>
       </c>
-      <c r="L80" s="77" t="s">
+      <c r="L80" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="M80" s="78" t="s">
+      <c r="M80" s="37" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="81" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J81" s="75" t="s">
+      <c r="J81" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="K81" s="76" t="s">
+      <c r="K81" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="L81" s="75" t="s">
+      <c r="L81" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="M81" s="76" t="s">
+      <c r="M81" s="35" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="82" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J82" s="77" t="s">
+      <c r="J82" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="K82" s="78" t="s">
+      <c r="K82" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="L82" s="77" t="s">
+      <c r="L82" s="36" t="s">
         <v>338</v>
       </c>
-      <c r="M82" s="78" t="s">
+      <c r="M82" s="37" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="83" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J83" s="75" t="s">
+      <c r="J83" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="K83" s="76" t="s">
+      <c r="K83" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="L83" s="75" t="s">
+      <c r="L83" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="M83" s="76" t="s">
+      <c r="M83" s="35" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="84" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J84" s="77" t="s">
+      <c r="J84" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="K84" s="78" t="s">
+      <c r="K84" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="L84" s="77" t="s">
+      <c r="L84" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="M84" s="78" t="s">
+      <c r="M84" s="37" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="85" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J85" s="75" t="s">
+      <c r="J85" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="K85" s="76" t="s">
+      <c r="K85" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="L85" s="75" t="s">
+      <c r="L85" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="M85" s="76" t="s">
+      <c r="M85" s="35" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="86" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J86" s="77" t="s">
+      <c r="J86" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="K86" s="78" t="s">
+      <c r="K86" s="37" t="s">
         <v>346</v>
       </c>
-      <c r="L86" s="77" t="s">
+      <c r="L86" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="M86" s="78" t="s">
+      <c r="M86" s="37" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="87" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J87" s="75" t="s">
+      <c r="J87" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="K87" s="76" t="s">
+      <c r="K87" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="L87" s="75" t="s">
+      <c r="L87" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="M87" s="76" t="s">
+      <c r="M87" s="35" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="88" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J88" s="77" t="s">
+      <c r="J88" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="K88" s="78" t="s">
+      <c r="K88" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="L88" s="77" t="s">
+      <c r="L88" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="M88" s="78" t="s">
+      <c r="M88" s="37" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="89" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J89" s="75" t="s">
+      <c r="J89" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="K89" s="76" t="s">
+      <c r="K89" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="L89" s="75" t="s">
+      <c r="L89" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="M89" s="76" t="s">
+      <c r="M89" s="35" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="90" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J90" s="77" t="s">
+      <c r="J90" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="K90" s="78" t="s">
+      <c r="K90" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="L90" s="77" t="s">
+      <c r="L90" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="M90" s="78" t="s">
+      <c r="M90" s="37" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="91" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J91" s="75" t="s">
+      <c r="J91" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="K91" s="76" t="s">
+      <c r="K91" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="L91" s="75" t="s">
+      <c r="L91" s="34" t="s">
         <v>361</v>
       </c>
-      <c r="M91" s="76" t="s">
+      <c r="M91" s="35" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="92" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J92" s="77" t="s">
+      <c r="J92" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="K92" s="78" t="s">
+      <c r="K92" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="L92" s="77" t="s">
+      <c r="L92" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="M92" s="78" t="s">
+      <c r="M92" s="37" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="93" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J93" s="75" t="s">
+      <c r="J93" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="K93" s="76" t="s">
+      <c r="K93" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="L93" s="75" t="s">
+      <c r="L93" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="M93" s="76" t="s">
+      <c r="M93" s="35" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="94" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J94" s="77" t="s">
+      <c r="J94" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="K94" s="78" t="s">
+      <c r="K94" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="L94" s="77" t="s">
+      <c r="L94" s="36" t="s">
         <v>369</v>
       </c>
-      <c r="M94" s="78" t="s">
+      <c r="M94" s="37" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="95" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J95" s="75" t="s">
+      <c r="J95" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="K95" s="76" t="s">
+      <c r="K95" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="L95" s="75" t="s">
+      <c r="L95" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="M95" s="76" t="s">
+      <c r="M95" s="35" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="96" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J96" s="77" t="s">
+      <c r="J96" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="K96" s="78" t="s">
+      <c r="K96" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="L96" s="77" t="s">
+      <c r="L96" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="M96" s="78" t="s">
+      <c r="M96" s="37" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="97" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J97" s="75" t="s">
+      <c r="J97" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="K97" s="76" t="s">
+      <c r="K97" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="L97" s="75" t="s">
+      <c r="L97" s="34" t="s">
         <v>375</v>
       </c>
-      <c r="M97" s="76" t="s">
+      <c r="M97" s="35" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="98" spans="10:13" x14ac:dyDescent="0.4">
-      <c r="J98" s="77" t="s">
+      <c r="J98" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="K98" s="78" t="s">
+      <c r="K98" s="37" t="s">
         <v>364</v>
       </c>
-      <c r="L98" s="77" t="s">
+      <c r="L98" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="M98" s="78" t="s">
+      <c r="M98" s="37" t="s">
         <v>378</v>
       </c>
     </row>
@@ -5951,64 +5961,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
     </row>
     <row r="2" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
     </row>
     <row r="3" spans="1:16" s="9" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -6672,64 +6682,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
     </row>
     <row r="2" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
     </row>
     <row r="3" spans="1:16" s="9" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -8566,64 +8576,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
     </row>
     <row r="2" spans="1:16" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
     </row>
     <row r="3" spans="1:16" s="9" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -9267,34 +9277,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:6" s="9" customFormat="1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
     </row>
     <row r="3" spans="1:6" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F4"/>
@@ -9616,37 +9626,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
     </row>
     <row r="2" spans="1:7" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="3" spans="1:7" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -10019,22 +10029,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="46"/>
     </row>
     <row r="2" spans="1:2" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="41"/>
+      <c r="B2" s="46"/>
     </row>
     <row r="3" spans="1:2" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="41"/>
+      <c r="B3" s="46"/>
     </row>
     <row r="5" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -11457,7 +11467,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>48</v>
       </c>
     </row>
@@ -11467,7 +11477,7 @@
       </c>
     </row>
     <row r="3" spans="1:1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>49</v>
       </c>
     </row>
@@ -12056,17 +12066,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="9" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="9" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="9" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>52</v>
       </c>
     </row>
